--- a/data/nzd0045/nzd0045.xlsx
+++ b/data/nzd0045/nzd0045.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O547"/>
+  <dimension ref="A1:O552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28339,6 +28339,261 @@
         <v>370.93</v>
       </c>
       <c r="O547" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>407.77</v>
+      </c>
+      <c r="C548" t="n">
+        <v>412.69</v>
+      </c>
+      <c r="D548" t="n">
+        <v>400.65</v>
+      </c>
+      <c r="E548" t="n">
+        <v>397.69</v>
+      </c>
+      <c r="F548" t="n">
+        <v>393.02</v>
+      </c>
+      <c r="G548" t="n">
+        <v>393.18</v>
+      </c>
+      <c r="H548" t="n">
+        <v>393.99</v>
+      </c>
+      <c r="I548" t="n">
+        <v>392.73</v>
+      </c>
+      <c r="J548" t="n">
+        <v>392.09</v>
+      </c>
+      <c r="K548" t="n">
+        <v>376.41</v>
+      </c>
+      <c r="L548" t="n">
+        <v>365.99</v>
+      </c>
+      <c r="M548" t="n">
+        <v>368.78</v>
+      </c>
+      <c r="N548" t="n">
+        <v>370.17</v>
+      </c>
+      <c r="O548" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>407.7</v>
+      </c>
+      <c r="C549" t="n">
+        <v>412.61</v>
+      </c>
+      <c r="D549" t="n">
+        <v>400.72</v>
+      </c>
+      <c r="E549" t="n">
+        <v>397.31</v>
+      </c>
+      <c r="F549" t="n">
+        <v>393.04</v>
+      </c>
+      <c r="G549" t="n">
+        <v>393.13</v>
+      </c>
+      <c r="H549" t="n">
+        <v>394.18</v>
+      </c>
+      <c r="I549" t="n">
+        <v>392.87</v>
+      </c>
+      <c r="J549" t="n">
+        <v>392.39</v>
+      </c>
+      <c r="K549" t="n">
+        <v>376.25</v>
+      </c>
+      <c r="L549" t="n">
+        <v>365.3</v>
+      </c>
+      <c r="M549" t="n">
+        <v>368.29</v>
+      </c>
+      <c r="N549" t="n">
+        <v>370.71</v>
+      </c>
+      <c r="O549" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>407.89</v>
+      </c>
+      <c r="C550" t="n">
+        <v>413.13</v>
+      </c>
+      <c r="D550" t="n">
+        <v>401.5</v>
+      </c>
+      <c r="E550" t="n">
+        <v>398.07</v>
+      </c>
+      <c r="F550" t="n">
+        <v>393.59</v>
+      </c>
+      <c r="G550" t="n">
+        <v>393.54</v>
+      </c>
+      <c r="H550" t="n">
+        <v>394.62</v>
+      </c>
+      <c r="I550" t="n">
+        <v>393.15</v>
+      </c>
+      <c r="J550" t="n">
+        <v>392.61</v>
+      </c>
+      <c r="K550" t="n">
+        <v>376.27</v>
+      </c>
+      <c r="L550" t="n">
+        <v>365.89</v>
+      </c>
+      <c r="M550" t="n">
+        <v>368.7</v>
+      </c>
+      <c r="N550" t="n">
+        <v>370.56</v>
+      </c>
+      <c r="O550" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>407.91</v>
+      </c>
+      <c r="C551" t="n">
+        <v>413.32</v>
+      </c>
+      <c r="D551" t="n">
+        <v>401.87</v>
+      </c>
+      <c r="E551" t="n">
+        <v>398.3</v>
+      </c>
+      <c r="F551" t="n">
+        <v>393.52</v>
+      </c>
+      <c r="G551" t="n">
+        <v>393.45</v>
+      </c>
+      <c r="H551" t="n">
+        <v>394.66</v>
+      </c>
+      <c r="I551" t="n">
+        <v>392.62</v>
+      </c>
+      <c r="J551" t="n">
+        <v>391.97</v>
+      </c>
+      <c r="K551" t="n">
+        <v>376.11</v>
+      </c>
+      <c r="L551" t="n">
+        <v>365.46</v>
+      </c>
+      <c r="M551" t="n">
+        <v>368.52</v>
+      </c>
+      <c r="N551" t="n">
+        <v>370.17</v>
+      </c>
+      <c r="O551" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>408.05</v>
+      </c>
+      <c r="C552" t="n">
+        <v>413.09</v>
+      </c>
+      <c r="D552" t="n">
+        <v>401.83</v>
+      </c>
+      <c r="E552" t="n">
+        <v>398.38</v>
+      </c>
+      <c r="F552" t="n">
+        <v>393.77</v>
+      </c>
+      <c r="G552" t="n">
+        <v>393.78</v>
+      </c>
+      <c r="H552" t="n">
+        <v>395.13</v>
+      </c>
+      <c r="I552" t="n">
+        <v>392.78</v>
+      </c>
+      <c r="J552" t="n">
+        <v>392.38</v>
+      </c>
+      <c r="K552" t="n">
+        <v>376.35</v>
+      </c>
+      <c r="L552" t="n">
+        <v>365.49</v>
+      </c>
+      <c r="M552" t="n">
+        <v>368.55</v>
+      </c>
+      <c r="N552" t="n">
+        <v>370.83</v>
+      </c>
+      <c r="O552" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28355,7 +28610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B551"/>
+  <dimension ref="A1:B556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33868,6 +34123,56 @@
       </c>
       <c r="B551" t="n">
         <v>0.88</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>-0.58</v>
       </c>
     </row>
   </sheetData>
@@ -34036,28 +34341,28 @@
         <v>0.1432</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1369969460662765</v>
+        <v>0.1462268106490354</v>
       </c>
       <c r="J2" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="K2" t="n">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05129041550397906</v>
+        <v>0.0584159007610201</v>
       </c>
       <c r="M2" t="n">
-        <v>3.389264167321841</v>
+        <v>3.405753523020214</v>
       </c>
       <c r="N2" t="n">
-        <v>20.78327620667166</v>
+        <v>20.85328609966825</v>
       </c>
       <c r="O2" t="n">
-        <v>4.558867864576869</v>
+        <v>4.566539838835117</v>
       </c>
       <c r="P2" t="n">
-        <v>398.7637189954197</v>
+        <v>398.6692435940603</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -34118,28 +34423,28 @@
         <v>0.1717</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1227746388076638</v>
+        <v>0.1275737681486941</v>
       </c>
       <c r="J3" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="K3" t="n">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04434773272268666</v>
+        <v>0.04844885598272675</v>
       </c>
       <c r="M3" t="n">
-        <v>3.334814262602376</v>
+        <v>3.324809141437506</v>
       </c>
       <c r="N3" t="n">
-        <v>19.44647859554246</v>
+        <v>19.3403275158627</v>
       </c>
       <c r="O3" t="n">
-        <v>4.409816163463332</v>
+        <v>4.397763922252159</v>
       </c>
       <c r="P3" t="n">
-        <v>406.847736472676</v>
+        <v>406.7986114886654</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34196,28 +34501,28 @@
         <v>0.1431</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1178399842104849</v>
+        <v>0.1180790667247944</v>
       </c>
       <c r="J4" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="K4" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06677321005621395</v>
+        <v>0.06825573534348206</v>
       </c>
       <c r="M4" t="n">
-        <v>2.52418756144882</v>
+        <v>2.505847342627367</v>
       </c>
       <c r="N4" t="n">
-        <v>11.59926681966404</v>
+        <v>11.49669283844301</v>
       </c>
       <c r="O4" t="n">
-        <v>3.405769636905004</v>
+        <v>3.390677342131364</v>
       </c>
       <c r="P4" t="n">
-        <v>398.0037421212191</v>
+        <v>398.0012871987889</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34274,28 +34579,28 @@
         <v>0.1071</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1208684422016891</v>
+        <v>0.1153424774239579</v>
       </c>
       <c r="J5" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="K5" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08280373658570517</v>
+        <v>0.07667005299851903</v>
       </c>
       <c r="M5" t="n">
-        <v>2.313848671209308</v>
+        <v>2.325374590941856</v>
       </c>
       <c r="N5" t="n">
-        <v>9.671602440294309</v>
+        <v>9.677857762850016</v>
       </c>
       <c r="O5" t="n">
-        <v>3.109920005449386</v>
+        <v>3.110925547622446</v>
       </c>
       <c r="P5" t="n">
-        <v>397.9379811711758</v>
+        <v>397.9945757228211</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34352,28 +34657,28 @@
         <v>0.1192</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06709904024825875</v>
+        <v>0.0569709846711977</v>
       </c>
       <c r="J6" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="K6" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01927429708234485</v>
+        <v>0.01392878894480731</v>
       </c>
       <c r="M6" t="n">
-        <v>2.965121571632963</v>
+        <v>3.002026343737214</v>
       </c>
       <c r="N6" t="n">
-        <v>13.69184172975892</v>
+        <v>13.87943857985005</v>
       </c>
       <c r="O6" t="n">
-        <v>3.700248874029816</v>
+        <v>3.725511854745607</v>
       </c>
       <c r="P6" t="n">
-        <v>397.519323143881</v>
+        <v>397.6230547984916</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34430,28 +34735,28 @@
         <v>0.1403</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1102296113280878</v>
+        <v>0.09513355842775746</v>
       </c>
       <c r="J7" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="K7" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03489995623520414</v>
+        <v>0.02586294404185907</v>
       </c>
       <c r="M7" t="n">
-        <v>3.518098060625705</v>
+        <v>3.5642984586607</v>
       </c>
       <c r="N7" t="n">
-        <v>20.0818745642212</v>
+        <v>20.59107940773776</v>
       </c>
       <c r="O7" t="n">
-        <v>4.481280460339566</v>
+        <v>4.537739460098801</v>
       </c>
       <c r="P7" t="n">
-        <v>399.3010073659659</v>
+        <v>399.4556238824695</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34508,28 +34813,28 @@
         <v>0.1456</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07510758087273758</v>
+        <v>0.06291928292430969</v>
       </c>
       <c r="J8" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="K8" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01351861108381081</v>
+        <v>0.009538342410107314</v>
       </c>
       <c r="M8" t="n">
-        <v>3.766535431754627</v>
+        <v>3.784952740435259</v>
       </c>
       <c r="N8" t="n">
-        <v>24.60280448056614</v>
+        <v>24.83143478098507</v>
       </c>
       <c r="O8" t="n">
-        <v>4.960121417925789</v>
+        <v>4.983114967666818</v>
       </c>
       <c r="P8" t="n">
-        <v>399.6411101215412</v>
+        <v>399.7659421796865</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34586,28 +34891,28 @@
         <v>0.1405</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05358190263636256</v>
+        <v>0.04030392752113796</v>
       </c>
       <c r="J9" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="K9" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00586377018501183</v>
+        <v>0.00333062815087859</v>
       </c>
       <c r="M9" t="n">
-        <v>4.066119670529052</v>
+        <v>4.091894235496392</v>
       </c>
       <c r="N9" t="n">
-        <v>29.09145661751428</v>
+        <v>29.36224299289362</v>
       </c>
       <c r="O9" t="n">
-        <v>5.393649656541875</v>
+        <v>5.418693845650778</v>
       </c>
       <c r="P9" t="n">
-        <v>399.1706661427346</v>
+        <v>399.3066642465587</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34664,28 +34969,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.008637104823229172</v>
+        <v>-0.007709117950056649</v>
       </c>
       <c r="J10" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="K10" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0001528107059969308</v>
+        <v>0.00012078124657533</v>
       </c>
       <c r="M10" t="n">
-        <v>4.328139367092451</v>
+        <v>4.376592612486731</v>
       </c>
       <c r="N10" t="n">
-        <v>29.1726897669173</v>
+        <v>29.71850386245858</v>
       </c>
       <c r="O10" t="n">
-        <v>5.401174850615123</v>
+        <v>5.451468046541095</v>
       </c>
       <c r="P10" t="n">
-        <v>401.6398886430646</v>
+        <v>401.8073122666382</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -34746,28 +35051,28 @@
         <v>0.1537</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1001678298760016</v>
+        <v>-0.1241539193661792</v>
       </c>
       <c r="J11" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="K11" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="L11" t="n">
-        <v>0.008588693975554285</v>
+        <v>0.01306438830853573</v>
       </c>
       <c r="M11" t="n">
-        <v>6.579358221314632</v>
+        <v>6.656681670944725</v>
       </c>
       <c r="N11" t="n">
-        <v>69.22189965205519</v>
+        <v>70.33801923986714</v>
       </c>
       <c r="O11" t="n">
-        <v>8.319969930958596</v>
+        <v>8.386776451048826</v>
       </c>
       <c r="P11" t="n">
-        <v>393.0406842607768</v>
+        <v>393.2863590589443</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -34828,28 +35133,28 @@
         <v>0.09320000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1404453885726913</v>
+        <v>-0.1783685016323265</v>
       </c>
       <c r="J12" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="K12" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="L12" t="n">
-        <v>0.008583987875846799</v>
+        <v>0.0136099817835188</v>
       </c>
       <c r="M12" t="n">
-        <v>9.537628381181317</v>
+        <v>9.636562846288012</v>
       </c>
       <c r="N12" t="n">
-        <v>136.1576497051007</v>
+        <v>139.2826365572244</v>
       </c>
       <c r="O12" t="n">
-        <v>11.66866100737787</v>
+        <v>11.80180649549993</v>
       </c>
       <c r="P12" t="n">
-        <v>391.6445861813598</v>
+        <v>392.0330098286472</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -34910,28 +35215,28 @@
         <v>0.0965</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2374970058633547</v>
+        <v>-0.277191140191376</v>
       </c>
       <c r="J13" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="K13" t="n">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01776654477602035</v>
+        <v>0.02391287333554126</v>
       </c>
       <c r="M13" t="n">
-        <v>11.30751266825498</v>
+        <v>11.38809057713094</v>
       </c>
       <c r="N13" t="n">
-        <v>185.6586359452176</v>
+        <v>188.7177497864876</v>
       </c>
       <c r="O13" t="n">
-        <v>13.62566093608738</v>
+        <v>13.7374579084519</v>
       </c>
       <c r="P13" t="n">
-        <v>398.1286017665648</v>
+        <v>398.5366638600439</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -34992,28 +35297,28 @@
         <v>0.1218</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2048391797681091</v>
+        <v>-0.2287695992302224</v>
       </c>
       <c r="J14" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="K14" t="n">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02458074402141319</v>
+        <v>0.03054399724971857</v>
       </c>
       <c r="M14" t="n">
-        <v>7.919879615379386</v>
+        <v>7.95243555996838</v>
       </c>
       <c r="N14" t="n">
-        <v>98.96472299429161</v>
+        <v>99.78821556787427</v>
       </c>
       <c r="O14" t="n">
-        <v>9.948101476879476</v>
+        <v>9.989405165868201</v>
       </c>
       <c r="P14" t="n">
-        <v>389.9670471449923</v>
+        <v>390.2132092749745</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -35055,7 +35360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O547"/>
+  <dimension ref="A1:O552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77157,6 +77462,391 @@
         </is>
       </c>
     </row>
+    <row r="548">
+      <c r="A548" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>-35.00686363771303,173.7798281775254</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>-35.00669802091509,173.78060925599456</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>-35.00647884874699,173.78141064674912</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>-35.00620659930572,173.78225195557198</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>-35.0059262081617,173.78308004376248</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>-35.00562384624721,173.78388536341174</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>-35.005263302278756,173.78463269735403</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>-35.004862074714495,173.78535186191718</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>-35.0044258330685,173.78601064044392</t>
+        </is>
+      </c>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>-35.003942516872854,173.78666243001902</t>
+        </is>
+      </c>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>-35.00343478688284,173.78733218306272</t>
+        </is>
+      </c>
+      <c r="M548" t="inlineStr">
+        <is>
+          <t>-35.002980872750186,173.78804096470705</t>
+        </is>
+      </c>
+      <c r="N548" t="inlineStr">
+        <is>
+          <t>-35.00254337374849,173.78875094755716</t>
+        </is>
+      </c>
+      <c r="O548" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>-35.00686425630926,173.7798283299476</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>-35.00669870056786,173.78060954974717</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>-35.00647828019257,173.78141031360545</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>-35.00620970465716,173.78225371558472</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>-35.00592604536704,173.78307994946812</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>-35.005624245784084,173.783885617274</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>-35.00526186450304,173.78463156513277</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>-35.00486107728073,173.78535092154524</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>-35.004423983704534,173.78600824119235</t>
+        </is>
+      </c>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>-35.00394340571025,173.78666381109733</t>
+        </is>
+      </c>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>-35.00343931652256,173.78733736657244</t>
+        </is>
+      </c>
+      <c r="M549" t="inlineStr">
+        <is>
+          <t>-35.00298443321562,173.78804414414978</t>
+        </is>
+      </c>
+      <c r="N549" t="inlineStr">
+        <is>
+          <t>-35.0025394498501,173.7887474438997</t>
+        </is>
+      </c>
+      <c r="O549" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>-35.00686257726237,173.7798279162302</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>-35.00669428282478,173.78060764035544</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>-35.00647194487182,173.78140660143373</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>-35.00620349395425,173.78225019555939</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>-35.00592156851385,173.783077356373</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>-35.00562096958173,173.78388353560342</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>-35.005258534917154,173.78462894314677</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>-35.00485908241319,173.78534904080144</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>-35.004422627504276,173.78600648174128</t>
+        </is>
+      </c>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>-35.00394329460558,173.78666363846256</t>
+        </is>
+      </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>-35.00343544335237,173.787332934296</t>
+        </is>
+      </c>
+      <c r="M550" t="inlineStr">
+        <is>
+          <t>-35.00298145405067,173.78804148379973</t>
+        </is>
+      </c>
+      <c r="N550" t="inlineStr">
+        <is>
+          <t>-35.00254053982188,173.78874841713784</t>
+        </is>
+      </c>
+      <c r="O550" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>-35.006862400520575,173.779827872681</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>-35.006692668649414,173.7806069426931</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>-35.00646893965552,173.78140484053196</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>-35.006201614399416,173.78224913028868</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>-35.00592213829516,173.7830776864033</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>-35.0056216887481,173.78388399255547</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>-35.00525823222752,173.78462870478444</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>-35.00486285841244,173.78535260078087</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>-35.00442657281406,173.7860116001446</t>
+        </is>
+      </c>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>-35.00394418344297,173.7866650195409</t>
+        </is>
+      </c>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>-35.00343826617133,173.78733616459914</t>
+        </is>
+      </c>
+      <c r="M551" t="inlineStr">
+        <is>
+          <t>-35.00298276197675,173.78804265175827</t>
+        </is>
+      </c>
+      <c r="N551" t="inlineStr">
+        <is>
+          <t>-35.00254337374849,173.78875094755716</t>
+        </is>
+      </c>
+      <c r="O551" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>-35.00686116332812,173.77982756783666</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>-35.00669462265117,173.78060778723173</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>-35.006469264543774,173.78140503089972</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>-35.006200960641195,173.78224875975974</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>-35.00592010336187,173.78307650772376</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>-35.00561905180473,173.7838823170646</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>-35.00525467562435,173.78462590402697</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>-35.00486171848815,173.78535152607006</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>-35.00442404535002,173.78600832116743</t>
+        </is>
+      </c>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>-35.003942850186874,173.7866629479234</t>
+        </is>
+      </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>-35.00343806923048,173.78733593922914</t>
+        </is>
+      </c>
+      <c r="M552" t="inlineStr">
+        <is>
+          <t>-35.00298254398908,173.78804245709853</t>
+        </is>
+      </c>
+      <c r="N552" t="inlineStr">
+        <is>
+          <t>-35.00253857787266,173.7887466653092</t>
+        </is>
+      </c>
+      <c r="O552" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0045/nzd0045.xlsx
+++ b/data/nzd0045/nzd0045.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O552"/>
+  <dimension ref="A1:O555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28596,6 +28596,159 @@
       <c r="O552" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>408.07</v>
+      </c>
+      <c r="C553" t="n">
+        <v>413.32</v>
+      </c>
+      <c r="D553" t="n">
+        <v>402.25</v>
+      </c>
+      <c r="E553" t="n">
+        <v>398.29</v>
+      </c>
+      <c r="F553" t="n">
+        <v>394.03</v>
+      </c>
+      <c r="G553" t="n">
+        <v>394.07</v>
+      </c>
+      <c r="H553" t="n">
+        <v>395.05</v>
+      </c>
+      <c r="I553" t="n">
+        <v>392.9</v>
+      </c>
+      <c r="J553" t="n">
+        <v>392.24</v>
+      </c>
+      <c r="K553" t="n">
+        <v>376.72</v>
+      </c>
+      <c r="L553" t="n">
+        <v>365.88</v>
+      </c>
+      <c r="M553" t="n">
+        <v>368.95</v>
+      </c>
+      <c r="N553" t="n">
+        <v>371.3</v>
+      </c>
+      <c r="O553" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>408.1</v>
+      </c>
+      <c r="C554" t="n">
+        <v>413.62</v>
+      </c>
+      <c r="D554" t="n">
+        <v>402.61</v>
+      </c>
+      <c r="E554" t="n">
+        <v>398.63</v>
+      </c>
+      <c r="F554" t="n">
+        <v>394.33</v>
+      </c>
+      <c r="G554" t="n">
+        <v>394.51</v>
+      </c>
+      <c r="H554" t="n">
+        <v>395.2</v>
+      </c>
+      <c r="I554" t="n">
+        <v>393.38</v>
+      </c>
+      <c r="J554" t="n">
+        <v>392.58</v>
+      </c>
+      <c r="K554" t="n">
+        <v>377.04</v>
+      </c>
+      <c r="L554" t="n">
+        <v>366.19</v>
+      </c>
+      <c r="M554" t="n">
+        <v>369.37</v>
+      </c>
+      <c r="N554" t="n">
+        <v>371.71</v>
+      </c>
+      <c r="O554" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>408.03</v>
+      </c>
+      <c r="C555" t="n">
+        <v>413.58</v>
+      </c>
+      <c r="D555" t="n">
+        <v>402.95</v>
+      </c>
+      <c r="E555" t="n">
+        <v>398.93</v>
+      </c>
+      <c r="F555" t="n">
+        <v>394.75</v>
+      </c>
+      <c r="G555" t="n">
+        <v>394.95</v>
+      </c>
+      <c r="H555" t="n">
+        <v>395.32</v>
+      </c>
+      <c r="I555" t="n">
+        <v>393.68</v>
+      </c>
+      <c r="J555" t="n">
+        <v>392.68</v>
+      </c>
+      <c r="K555" t="n">
+        <v>377.2</v>
+      </c>
+      <c r="L555" t="n">
+        <v>366.43</v>
+      </c>
+      <c r="M555" t="n">
+        <v>369.45</v>
+      </c>
+      <c r="N555" t="n">
+        <v>371.82</v>
+      </c>
+      <c r="O555" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -28610,7 +28763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B556"/>
+  <dimension ref="A1:B559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34173,6 +34326,36 @@
       </c>
       <c r="B556" t="n">
         <v>-0.58</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -34341,28 +34524,28 @@
         <v>0.1432</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1462268106490354</v>
+        <v>0.1517370329604281</v>
       </c>
       <c r="J2" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="K2" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0584159007610201</v>
+        <v>0.06285567555380289</v>
       </c>
       <c r="M2" t="n">
-        <v>3.405753523020214</v>
+        <v>3.415676970383589</v>
       </c>
       <c r="N2" t="n">
-        <v>20.85328609966825</v>
+        <v>20.89851562363425</v>
       </c>
       <c r="O2" t="n">
-        <v>4.566539838835117</v>
+        <v>4.571489431644161</v>
       </c>
       <c r="P2" t="n">
-        <v>398.6692435940603</v>
+        <v>398.6126817872976</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -34423,28 +34606,28 @@
         <v>0.1717</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1275737681486941</v>
+        <v>0.1308758864558303</v>
       </c>
       <c r="J3" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="K3" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04844885598272675</v>
+        <v>0.05127933513737604</v>
       </c>
       <c r="M3" t="n">
-        <v>3.324809141437506</v>
+        <v>3.320865496874894</v>
       </c>
       <c r="N3" t="n">
-        <v>19.3403275158627</v>
+        <v>19.29236772109912</v>
       </c>
       <c r="O3" t="n">
-        <v>4.397763922252159</v>
+        <v>4.39230778988667</v>
       </c>
       <c r="P3" t="n">
-        <v>406.7986114886654</v>
+        <v>406.7647149008079</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34501,28 +34684,28 @@
         <v>0.1431</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1180790667247944</v>
+        <v>0.1195116613123974</v>
       </c>
       <c r="J4" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="K4" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06825573534348206</v>
+        <v>0.07049982439594171</v>
       </c>
       <c r="M4" t="n">
-        <v>2.505847342627367</v>
+        <v>2.498507959791049</v>
       </c>
       <c r="N4" t="n">
-        <v>11.49669283844301</v>
+        <v>11.44554617558248</v>
       </c>
       <c r="O4" t="n">
-        <v>3.390677342131364</v>
+        <v>3.383126686304029</v>
       </c>
       <c r="P4" t="n">
-        <v>398.0012871987889</v>
+        <v>397.9865698167816</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34579,28 +34762,28 @@
         <v>0.1071</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1153424774239579</v>
+        <v>0.1128258590461805</v>
       </c>
       <c r="J5" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="K5" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07667005299851903</v>
+        <v>0.07416246364685786</v>
       </c>
       <c r="M5" t="n">
-        <v>2.325374590941856</v>
+        <v>2.327523914169177</v>
       </c>
       <c r="N5" t="n">
-        <v>9.677857762850016</v>
+        <v>9.65878385865129</v>
       </c>
       <c r="O5" t="n">
-        <v>3.110925547622446</v>
+        <v>3.107858403893474</v>
       </c>
       <c r="P5" t="n">
-        <v>397.9945757228211</v>
+        <v>398.0204231560928</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34657,28 +34840,28 @@
         <v>0.1192</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0569709846711977</v>
+        <v>0.05212724240968749</v>
       </c>
       <c r="J6" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="K6" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01392878894480731</v>
+        <v>0.01171954600713077</v>
       </c>
       <c r="M6" t="n">
-        <v>3.002026343737214</v>
+        <v>3.016502383366656</v>
       </c>
       <c r="N6" t="n">
-        <v>13.87943857985005</v>
+        <v>13.92686716891144</v>
       </c>
       <c r="O6" t="n">
-        <v>3.725511854745607</v>
+        <v>3.731871804994304</v>
       </c>
       <c r="P6" t="n">
-        <v>397.6230547984916</v>
+        <v>397.6728049796403</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34735,28 +34918,28 @@
         <v>0.1403</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09513355842775746</v>
+        <v>0.08753482776156818</v>
       </c>
       <c r="J7" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="K7" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02586294404185907</v>
+        <v>0.02191940560777472</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5642984586607</v>
+        <v>3.586849597601672</v>
       </c>
       <c r="N7" t="n">
-        <v>20.59107940773776</v>
+        <v>20.78079443039243</v>
       </c>
       <c r="O7" t="n">
-        <v>4.537739460098801</v>
+        <v>4.558595664280002</v>
       </c>
       <c r="P7" t="n">
-        <v>399.4556238824695</v>
+        <v>399.5336716458771</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34813,28 +34996,28 @@
         <v>0.1456</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06291928292430969</v>
+        <v>0.05657551823564107</v>
       </c>
       <c r="J8" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="K8" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009538342410107314</v>
+        <v>0.007750336546530678</v>
       </c>
       <c r="M8" t="n">
-        <v>3.784952740435259</v>
+        <v>3.792801176030237</v>
       </c>
       <c r="N8" t="n">
-        <v>24.83143478098507</v>
+        <v>24.90645939444325</v>
       </c>
       <c r="O8" t="n">
-        <v>4.983114967666818</v>
+        <v>4.99063717319174</v>
       </c>
       <c r="P8" t="n">
-        <v>399.7659421796865</v>
+        <v>399.8311016506642</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34891,28 +35074,28 @@
         <v>0.1405</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04030392752113796</v>
+        <v>0.03314989904720129</v>
       </c>
       <c r="J9" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="K9" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00333062815087859</v>
+        <v>0.002261274109125355</v>
       </c>
       <c r="M9" t="n">
-        <v>4.091894235496392</v>
+        <v>4.104137016335316</v>
       </c>
       <c r="N9" t="n">
-        <v>29.36224299289362</v>
+        <v>29.47016402855344</v>
       </c>
       <c r="O9" t="n">
-        <v>5.418693845650778</v>
+        <v>5.428642926971108</v>
       </c>
       <c r="P9" t="n">
-        <v>399.3066642465587</v>
+        <v>399.3801447889449</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34969,28 +35152,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.007709117950056649</v>
+        <v>-0.01691116079876824</v>
       </c>
       <c r="J10" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="K10" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="L10" t="n">
-        <v>0.00012078124657533</v>
+        <v>0.0005790969936194656</v>
       </c>
       <c r="M10" t="n">
-        <v>4.376592612486731</v>
+        <v>4.40209343625876</v>
       </c>
       <c r="N10" t="n">
-        <v>29.71850386245858</v>
+        <v>29.99842613984412</v>
       </c>
       <c r="O10" t="n">
-        <v>5.451468046541095</v>
+        <v>5.477081900048978</v>
       </c>
       <c r="P10" t="n">
-        <v>401.8073122666382</v>
+        <v>401.9018303378882</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -35051,28 +35234,28 @@
         <v>0.1537</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1241539193661792</v>
+        <v>-0.13725080150441</v>
       </c>
       <c r="J11" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="K11" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01306438830853573</v>
+        <v>0.0159031245715876</v>
       </c>
       <c r="M11" t="n">
-        <v>6.656681670944725</v>
+        <v>6.698342002546072</v>
       </c>
       <c r="N11" t="n">
-        <v>70.33801923986714</v>
+        <v>70.84997225311679</v>
       </c>
       <c r="O11" t="n">
-        <v>8.386776451048826</v>
+        <v>8.417242556390827</v>
       </c>
       <c r="P11" t="n">
-        <v>393.2863590589443</v>
+        <v>393.4208829944967</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -35133,28 +35316,28 @@
         <v>0.09320000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1783685016323265</v>
+        <v>-0.199665173767603</v>
       </c>
       <c r="J12" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="K12" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0136099817835188</v>
+        <v>0.01690739846173761</v>
       </c>
       <c r="M12" t="n">
-        <v>9.636562846288012</v>
+        <v>9.690407425106416</v>
       </c>
       <c r="N12" t="n">
-        <v>139.2826365572244</v>
+        <v>140.8889052775416</v>
       </c>
       <c r="O12" t="n">
-        <v>11.80180649549993</v>
+        <v>11.86966323353538</v>
       </c>
       <c r="P12" t="n">
-        <v>392.0330098286472</v>
+        <v>392.2517580405228</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -35215,28 +35398,28 @@
         <v>0.0965</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.277191140191376</v>
+        <v>-0.2993454880869081</v>
       </c>
       <c r="J13" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="K13" t="n">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02391287333554126</v>
+        <v>0.02772880212662554</v>
       </c>
       <c r="M13" t="n">
-        <v>11.38809057713094</v>
+        <v>11.42967379349432</v>
       </c>
       <c r="N13" t="n">
-        <v>188.7177497864876</v>
+        <v>190.2322609338341</v>
       </c>
       <c r="O13" t="n">
-        <v>13.7374579084519</v>
+        <v>13.79247116849747</v>
       </c>
       <c r="P13" t="n">
-        <v>398.5366638600439</v>
+        <v>398.7650604720026</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -35297,28 +35480,28 @@
         <v>0.1218</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2287695992302224</v>
+        <v>-0.2414048590982986</v>
       </c>
       <c r="J14" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="K14" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03054399724971857</v>
+        <v>0.03400399012131017</v>
       </c>
       <c r="M14" t="n">
-        <v>7.95243555996838</v>
+        <v>7.964447672848769</v>
       </c>
       <c r="N14" t="n">
-        <v>99.78821556787427</v>
+        <v>100.0714847569238</v>
       </c>
       <c r="O14" t="n">
-        <v>9.989405165868201</v>
+        <v>10.00357359931559</v>
       </c>
       <c r="P14" t="n">
-        <v>390.2132092749745</v>
+        <v>390.3435507169728</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -35360,7 +35543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O552"/>
+  <dimension ref="A1:O555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77847,6 +78030,237 @@
         </is>
       </c>
     </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>-35.00686098658633,173.77982752428744</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>-35.006692668649414,173.7806069426931</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>-35.00646585321713,173.78140303203836</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>-35.00620169611919,173.7822491766048</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>-35.005917987031246,173.7830752818971</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>-35.005616734490836,173.78388084466366</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>-35.00525528100361,173.7846263807516</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>-35.00486086354492,173.78535072003697</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>-35.00442490838653,173.78600944081813</t>
+        </is>
+      </c>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>-35.003940794750314,173.78665975417988</t>
+        </is>
+      </c>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>-35.00343550899934,173.7873330094193</t>
+        </is>
+      </c>
+      <c r="M553" t="inlineStr">
+        <is>
+          <t>-35.00297963748664,173.78803986163516</t>
+        </is>
+      </c>
+      <c r="N553" t="inlineStr">
+        <is>
+          <t>-35.00253516262763,173.7887436158299</t>
+        </is>
+      </c>
+      <c r="O553" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>-35.00686072147368,173.77982745896367</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>-35.00669011995144,173.7806058411211</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>-35.00646292922283,173.7814013187288</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>-35.00619891764679,173.78224760185685</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>-35.00591554511128,173.78307386748185</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>-35.00561321856627,173.7838786106761</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>-35.00525414591747,173.7846254868929</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>-35.004857443771975,173.7853474959048</t>
+        </is>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>-35.00442281244067,173.7860067216664</t>
+        </is>
+      </c>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>-35.00393901707539,173.78665699202347</t>
+        </is>
+      </c>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>-35.00343347394376,173.78733068059623</t>
+        </is>
+      </c>
+      <c r="M554" t="inlineStr">
+        <is>
+          <t>-35.00297658565901,173.7880371363988</t>
+        </is>
+      </c>
+      <c r="N554" t="inlineStr">
+        <is>
+          <t>-35.00253218337129,173.78874095564606</t>
+        </is>
+      </c>
+      <c r="O554" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>-35.006861340069904,173.77982761138585</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>-35.00669045977785,173.78060598799735</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>-35.00646016767264,173.7813997006032</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>-35.00619646605348,173.78224621237348</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>-35.005912126423276,173.78307188730062</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>-35.005609702641635,173.7838763766888</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>-35.00525323784857,173.7846247718059</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>-35.00485530641383,173.78534548082237</t>
+        </is>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>-35.004422195985995,173.78600592191594</t>
+        </is>
+      </c>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>-35.0039381282379,173.7866556109453</t>
+        </is>
+      </c>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>-35.003431898416814,173.78732887763653</t>
+        </is>
+      </c>
+      <c r="M555" t="inlineStr">
+        <is>
+          <t>-35.00297600435851,173.7880366173062</t>
+        </is>
+      </c>
+      <c r="N555" t="inlineStr">
+        <is>
+          <t>-35.00253138405861,173.78874024193823</t>
+        </is>
+      </c>
+      <c r="O555" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0045/nzd0045.xlsx
+++ b/data/nzd0045/nzd0045.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O555"/>
+  <dimension ref="A1:O557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28749,6 +28749,108 @@
       <c r="O555" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>408.25</v>
+      </c>
+      <c r="C556" t="n">
+        <v>413.48</v>
+      </c>
+      <c r="D556" t="n">
+        <v>402.93</v>
+      </c>
+      <c r="E556" t="n">
+        <v>398.92</v>
+      </c>
+      <c r="F556" t="n">
+        <v>394.68</v>
+      </c>
+      <c r="G556" t="n">
+        <v>394.98</v>
+      </c>
+      <c r="H556" t="n">
+        <v>395.13</v>
+      </c>
+      <c r="I556" t="n">
+        <v>393.71</v>
+      </c>
+      <c r="J556" t="n">
+        <v>392.6</v>
+      </c>
+      <c r="K556" t="n">
+        <v>376.95</v>
+      </c>
+      <c r="L556" t="n">
+        <v>366.1</v>
+      </c>
+      <c r="M556" t="n">
+        <v>368.61</v>
+      </c>
+      <c r="N556" t="n">
+        <v>371.01</v>
+      </c>
+      <c r="O556" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>407.48</v>
+      </c>
+      <c r="C557" t="n">
+        <v>413.07</v>
+      </c>
+      <c r="D557" t="n">
+        <v>402.67</v>
+      </c>
+      <c r="E557" t="n">
+        <v>398.64</v>
+      </c>
+      <c r="F557" t="n">
+        <v>394.45</v>
+      </c>
+      <c r="G557" t="n">
+        <v>394.86</v>
+      </c>
+      <c r="H557" t="n">
+        <v>394.91</v>
+      </c>
+      <c r="I557" t="n">
+        <v>393.38</v>
+      </c>
+      <c r="J557" t="n">
+        <v>392.49</v>
+      </c>
+      <c r="K557" t="n">
+        <v>376.83</v>
+      </c>
+      <c r="L557" t="n">
+        <v>365.79</v>
+      </c>
+      <c r="M557" t="n">
+        <v>368.42</v>
+      </c>
+      <c r="N557" t="n">
+        <v>370.94</v>
+      </c>
+      <c r="O557" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -28763,7 +28865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B559"/>
+  <dimension ref="A1:B561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34356,6 +34458,26 @@
       </c>
       <c r="B559" t="n">
         <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>-0.54</v>
       </c>
     </row>
   </sheetData>
@@ -34524,28 +34646,28 @@
         <v>0.1432</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1517370329604281</v>
+        <v>0.155190866365847</v>
       </c>
       <c r="J2" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="K2" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06285567555380289</v>
+        <v>0.06575273254924141</v>
       </c>
       <c r="M2" t="n">
-        <v>3.415676970383589</v>
+        <v>3.421091772782083</v>
       </c>
       <c r="N2" t="n">
-        <v>20.89851562363425</v>
+        <v>20.91816348838971</v>
       </c>
       <c r="O2" t="n">
-        <v>4.571489431644161</v>
+        <v>4.573637883391044</v>
       </c>
       <c r="P2" t="n">
-        <v>398.6126817872976</v>
+        <v>398.5771094026441</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -34606,28 +34728,28 @@
         <v>0.1717</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1308758864558303</v>
+        <v>0.1328693285508867</v>
       </c>
       <c r="J3" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="K3" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05127933513737604</v>
+        <v>0.05307349503520775</v>
       </c>
       <c r="M3" t="n">
-        <v>3.320865496874894</v>
+        <v>3.317343062607976</v>
       </c>
       <c r="N3" t="n">
-        <v>19.29236772109912</v>
+        <v>19.25445688186525</v>
       </c>
       <c r="O3" t="n">
-        <v>4.39230778988667</v>
+        <v>4.387990073127473</v>
       </c>
       <c r="P3" t="n">
-        <v>406.7647149008079</v>
+        <v>406.7441836529245</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34684,28 +34806,28 @@
         <v>0.1431</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1195116613123974</v>
+        <v>0.1205720838882343</v>
       </c>
       <c r="J4" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="K4" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07049982439594171</v>
+        <v>0.0721276751562302</v>
       </c>
       <c r="M4" t="n">
-        <v>2.498507959791049</v>
+        <v>2.494193062343914</v>
       </c>
       <c r="N4" t="n">
-        <v>11.44554617558248</v>
+        <v>11.41332043390104</v>
       </c>
       <c r="O4" t="n">
-        <v>3.383126686304029</v>
+        <v>3.378360613359835</v>
       </c>
       <c r="P4" t="n">
-        <v>397.9865698167816</v>
+        <v>397.975641172624</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34762,28 +34884,28 @@
         <v>0.1071</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1128258590461805</v>
+        <v>0.1112874809512863</v>
       </c>
       <c r="J5" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="K5" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07416246364685786</v>
+        <v>0.07268561759122472</v>
       </c>
       <c r="M5" t="n">
-        <v>2.327523914169177</v>
+        <v>2.328138166035897</v>
       </c>
       <c r="N5" t="n">
-        <v>9.65878385865129</v>
+        <v>9.642803655774383</v>
       </c>
       <c r="O5" t="n">
-        <v>3.107858403893474</v>
+        <v>3.105286404790125</v>
       </c>
       <c r="P5" t="n">
-        <v>398.0204231560928</v>
+        <v>398.0362777219075</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34840,28 +34962,28 @@
         <v>0.1192</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05212724240968749</v>
+        <v>0.0490931140296589</v>
       </c>
       <c r="J6" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="K6" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01171954600713077</v>
+        <v>0.01043418219546488</v>
       </c>
       <c r="M6" t="n">
-        <v>3.016502383366656</v>
+        <v>3.025110130940146</v>
       </c>
       <c r="N6" t="n">
-        <v>13.92686716891144</v>
+        <v>13.9495314342774</v>
       </c>
       <c r="O6" t="n">
-        <v>3.731871804994304</v>
+        <v>3.734907152029003</v>
       </c>
       <c r="P6" t="n">
-        <v>397.6728049796403</v>
+        <v>397.7040747178769</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34918,28 +35040,28 @@
         <v>0.1403</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08753482776156818</v>
+        <v>0.0828510555269724</v>
       </c>
       <c r="J7" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="K7" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02191940560777472</v>
+        <v>0.01966909528589833</v>
       </c>
       <c r="M7" t="n">
-        <v>3.586849597601672</v>
+        <v>3.600573648532874</v>
       </c>
       <c r="N7" t="n">
-        <v>20.78079443039243</v>
+        <v>20.87933152373389</v>
       </c>
       <c r="O7" t="n">
-        <v>4.558595664280002</v>
+        <v>4.569390716904595</v>
       </c>
       <c r="P7" t="n">
-        <v>399.5336716458771</v>
+        <v>399.5819425683202</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34996,28 +35118,28 @@
         <v>0.1456</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05657551823564107</v>
+        <v>0.05231951981557495</v>
       </c>
       <c r="J8" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="K8" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L8" t="n">
-        <v>0.007750336546530678</v>
+        <v>0.006648419906810199</v>
       </c>
       <c r="M8" t="n">
-        <v>3.792801176030237</v>
+        <v>3.798703688350436</v>
       </c>
       <c r="N8" t="n">
-        <v>24.90645939444325</v>
+        <v>24.95998003224192</v>
       </c>
       <c r="O8" t="n">
-        <v>4.99063717319174</v>
+        <v>4.995996400343171</v>
       </c>
       <c r="P8" t="n">
-        <v>399.8311016506642</v>
+        <v>399.8749639630025</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35074,28 +35196,28 @@
         <v>0.1405</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03314989904720129</v>
+        <v>0.02863231713432782</v>
       </c>
       <c r="J9" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="K9" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002261274109125355</v>
+        <v>0.001691661034448844</v>
       </c>
       <c r="M9" t="n">
-        <v>4.104137016335316</v>
+        <v>4.111034680001524</v>
       </c>
       <c r="N9" t="n">
-        <v>29.47016402855344</v>
+        <v>29.52545053405856</v>
       </c>
       <c r="O9" t="n">
-        <v>5.428642926971108</v>
+        <v>5.433732652059591</v>
       </c>
       <c r="P9" t="n">
-        <v>399.3801447889449</v>
+        <v>399.4267030016393</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35152,28 +35274,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.01691116079876824</v>
+        <v>-0.02288347206026017</v>
       </c>
       <c r="J10" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="K10" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0005790969936194656</v>
+        <v>0.001058055504902344</v>
       </c>
       <c r="M10" t="n">
-        <v>4.40209343625876</v>
+        <v>4.417927384378454</v>
       </c>
       <c r="N10" t="n">
-        <v>29.99842613984412</v>
+        <v>30.17225895171638</v>
       </c>
       <c r="O10" t="n">
-        <v>5.477081900048978</v>
+        <v>5.492928085430973</v>
       </c>
       <c r="P10" t="n">
-        <v>401.9018303378882</v>
+        <v>401.9633809268092</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -35234,28 +35356,28 @@
         <v>0.1537</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.13725080150441</v>
+        <v>-0.1458505876080224</v>
       </c>
       <c r="J11" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="K11" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0159031245715876</v>
+        <v>0.01791205361236059</v>
       </c>
       <c r="M11" t="n">
-        <v>6.698342002546072</v>
+        <v>6.72526469687678</v>
       </c>
       <c r="N11" t="n">
-        <v>70.84997225311679</v>
+        <v>71.17927426309058</v>
       </c>
       <c r="O11" t="n">
-        <v>8.417242556390827</v>
+        <v>8.436781036810816</v>
       </c>
       <c r="P11" t="n">
-        <v>393.4208829944967</v>
+        <v>393.5095123053378</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -35316,28 +35438,28 @@
         <v>0.09320000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.199665173767603</v>
+        <v>-0.2136934934201937</v>
       </c>
       <c r="J12" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="K12" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01690739846173761</v>
+        <v>0.0192564364109401</v>
       </c>
       <c r="M12" t="n">
-        <v>9.690407425106416</v>
+        <v>9.725882236608829</v>
       </c>
       <c r="N12" t="n">
-        <v>140.8889052775416</v>
+        <v>141.93657901642</v>
       </c>
       <c r="O12" t="n">
-        <v>11.86966323353538</v>
+        <v>11.91371390526145</v>
       </c>
       <c r="P12" t="n">
-        <v>392.2517580405228</v>
+        <v>392.3963337916123</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -35398,28 +35520,28 @@
         <v>0.0965</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2993454880869081</v>
+        <v>-0.3142794923088064</v>
       </c>
       <c r="J13" t="n">
+        <v>556</v>
+      </c>
+      <c r="K13" t="n">
         <v>554</v>
       </c>
-      <c r="K13" t="n">
-        <v>552</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.02772880212662554</v>
+        <v>0.03043412306363402</v>
       </c>
       <c r="M13" t="n">
-        <v>11.42967379349432</v>
+        <v>11.45827236028896</v>
       </c>
       <c r="N13" t="n">
-        <v>190.2322609338341</v>
+        <v>191.2972927849417</v>
       </c>
       <c r="O13" t="n">
-        <v>13.79247116849747</v>
+        <v>13.83102645449504</v>
       </c>
       <c r="P13" t="n">
-        <v>398.7650604720026</v>
+        <v>398.9195362323431</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -35480,28 +35602,28 @@
         <v>0.1218</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2414048590982986</v>
+        <v>-0.2500624939721051</v>
       </c>
       <c r="J14" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="K14" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03400399012131017</v>
+        <v>0.03646098156327215</v>
       </c>
       <c r="M14" t="n">
-        <v>7.964447672848769</v>
+        <v>7.973406768218548</v>
       </c>
       <c r="N14" t="n">
-        <v>100.0714847569238</v>
+        <v>100.2982991769149</v>
       </c>
       <c r="O14" t="n">
-        <v>10.00357359931559</v>
+        <v>10.01490385260462</v>
       </c>
       <c r="P14" t="n">
-        <v>390.3435507169728</v>
+        <v>390.4331591490268</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -35543,7 +35665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O555"/>
+  <dimension ref="A1:O557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78261,6 +78383,160 @@
         </is>
       </c>
     </row>
+    <row r="556">
+      <c r="A556" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>-35.00685939591032,173.7798271323447</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>-35.00669130934383,173.780606355188</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>-35.00646033011679,173.78139979578705</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>-35.00619654777324,173.78224625868958</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>-35.00591269620462,173.7830722173308</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>-35.0056094629195,173.78387622437148</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>-35.00525467562435,173.78462590402697</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>-35.004855092678,173.78534527931413</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>-35.00442268914974,173.78600656171633</t>
+        </is>
+      </c>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>-35.00393951704647,173.78665776887996</t>
+        </is>
+      </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>-35.003434064766346,173.78733135670618</t>
+        </is>
+      </c>
+      <c r="M556" t="inlineStr">
+        <is>
+          <t>-35.00298210801371,173.788042067779</t>
+        </is>
+      </c>
+      <c r="N556" t="inlineStr">
+        <is>
+          <t>-35.0025372699065,173.7887454974235</t>
+        </is>
+      </c>
+      <c r="O556" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>-35.00686620046882,173.7798288089888</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>-35.006694792564375,173.78060786066985</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>-35.00646244189044,173.7814010331772</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>-35.006198835927016,173.78224755554072</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>-35.00591456834327,173.78307330171575</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>-35.00561042180804,173.78387683364073</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>-35.00525634041733,173.7846272150198</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>-35.004857443771975,173.7853474959048</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>-35.004423367249885,173.78600744144185</t>
+        </is>
+      </c>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>-35.003940183674565,173.78665880468859</t>
+        </is>
+      </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>-35.00343609982192,173.78733368552923</t>
+        </is>
+      </c>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>-35.002983488602354,173.78804330062414</t>
+        </is>
+      </c>
+      <c r="N557" t="inlineStr">
+        <is>
+          <t>-35.00253777856001,173.78874595160124</t>
+        </is>
+      </c>
+      <c r="O557" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
